--- a/EX1/CPa results/CPa_for_CodeBERT4JIT_test_data.xlsx
+++ b/EX1/CPa results/CPa_for_CodeBERT4JIT_test_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xhulj\Desktop\CPa\EX1\CP_res\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xhulj\Desktop\CPa\EX1\CPa results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC6EF441-1F79-48C5-9E8A-09F5BD5DCF87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3D16492-55C9-4AB1-A62D-78057891E582}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="35600" yWindow="6550" windowWidth="17400" windowHeight="14110" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="47550" yWindow="3240" windowWidth="17295" windowHeight="13770" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="OP_0.05" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="23">
   <si>
     <t>Total correct made 
 by CodeBERT4JIT</t>
@@ -91,12 +91,30 @@
   <si>
     <t>recall</t>
   </si>
+  <si>
+    <t>Precision_clean</t>
+  </si>
+  <si>
+    <t>recall_clean</t>
+  </si>
+  <si>
+    <t>Precision faulty</t>
+  </si>
+  <si>
+    <t>recall_faulty</t>
+  </si>
+  <si>
+    <t>CodeBERT4JIT with openstack makes 1144 correct predictions, where 1111 are clean and 33 fault prone</t>
+  </si>
+  <si>
+    <t>CodeBERT4JIT with QT makes 2355 correct predictions; 2326  clean, 29 fault-prone</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -155,6 +173,19 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -206,7 +237,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -238,6 +269,14 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -366,16 +405,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O12"/>
+  <dimension ref="A1:U16"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.5546875" style="2" customWidth="1"/>
     <col min="2" max="6" width="12.6640625" style="1"/>
     <col min="7" max="7" width="24.21875" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="12.6640625" style="1"/>
+    <col min="8" max="16" width="12.6640625" style="1"/>
+    <col min="22" max="16384" width="12.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -419,8 +459,20 @@
       <c r="O1" s="5" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="R1" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1144</v>
       </c>
@@ -459,15 +511,31 @@
       </c>
       <c r="M2"/>
       <c r="N2">
-        <f t="shared" ref="N2:N9" si="0">G2/E2</f>
+        <f>G2/E2</f>
         <v>0.92623814541622762</v>
       </c>
       <c r="O2">
-        <f t="shared" ref="O2:O9" si="1">G2/A2</f>
+        <f t="shared" ref="O2:O9" si="0">G2/A2</f>
         <v>0.76835664335664333</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q2">
+        <f>J2/(J2+K2)</f>
+        <v>0.93254817987152039</v>
+      </c>
+      <c r="R2">
+        <f>J2/1111</f>
+        <v>0.78397839783978396</v>
+      </c>
+      <c r="T2">
+        <f>I2/(I2+L2)</f>
+        <v>0.53333333333333333</v>
+      </c>
+      <c r="U2">
+        <f>I2/33</f>
+        <v>0.24242424242424243</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1144</v>
       </c>
@@ -506,15 +574,31 @@
       </c>
       <c r="M3"/>
       <c r="N3">
+        <f t="shared" ref="N2:N9" si="1">G3/E3</f>
+        <v>0.92645654250238774</v>
+      </c>
+      <c r="O3">
         <f t="shared" si="0"/>
-        <v>0.92645654250238774</v>
-      </c>
-      <c r="O3">
-        <f t="shared" si="1"/>
         <v>0.84790209790209792</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q3">
+        <f t="shared" ref="Q3:Q11" si="2">J3/(J3+K3)</f>
+        <v>0.93230174081237915</v>
+      </c>
+      <c r="R3">
+        <f t="shared" ref="R3:R11" si="3">J3/1111</f>
+        <v>0.86768676867686767</v>
+      </c>
+      <c r="T3">
+        <f t="shared" ref="T3:T11" si="4">I3/(I3+L3)</f>
+        <v>0.46153846153846156</v>
+      </c>
+      <c r="U3">
+        <f t="shared" ref="U3:U11" si="5">I3/33</f>
+        <v>0.18181818181818182</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1144</v>
       </c>
@@ -553,15 +637,31 @@
       </c>
       <c r="M4"/>
       <c r="N4">
+        <f t="shared" si="1"/>
+        <v>0.92216216216216218</v>
+      </c>
+      <c r="O4">
         <f t="shared" si="0"/>
-        <v>0.92216216216216218</v>
-      </c>
-      <c r="O4">
-        <f t="shared" si="1"/>
         <v>0.74562937062937062</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q4">
+        <f t="shared" si="2"/>
+        <v>0.92274211099020675</v>
+      </c>
+      <c r="R4">
+        <f t="shared" si="3"/>
+        <v>0.76327632763276332</v>
+      </c>
+      <c r="T4">
+        <f t="shared" si="4"/>
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="U4">
+        <f t="shared" si="5"/>
+        <v>0.15151515151515152</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1144</v>
       </c>
@@ -600,15 +700,31 @@
       </c>
       <c r="M5"/>
       <c r="N5">
+        <f t="shared" si="1"/>
+        <v>0.93339960238568587</v>
+      </c>
+      <c r="O5">
         <f t="shared" si="0"/>
-        <v>0.93339960238568587</v>
-      </c>
-      <c r="O5">
-        <f t="shared" si="1"/>
         <v>0.82080419580419584</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q5">
+        <f t="shared" si="2"/>
+        <v>0.93951612903225812</v>
+      </c>
+      <c r="R5">
+        <f t="shared" si="3"/>
+        <v>0.83888388838883887</v>
+      </c>
+      <c r="T5">
+        <f t="shared" si="4"/>
+        <v>0.5</v>
+      </c>
+      <c r="U5">
+        <f t="shared" si="5"/>
+        <v>0.21212121212121213</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1144</v>
       </c>
@@ -647,15 +763,31 @@
       </c>
       <c r="M6"/>
       <c r="N6">
+        <f t="shared" si="1"/>
+        <v>0.91902439024390248</v>
+      </c>
+      <c r="O6">
         <f t="shared" si="0"/>
-        <v>0.91902439024390248</v>
-      </c>
-      <c r="O6">
-        <f t="shared" si="1"/>
         <v>0.82342657342657344</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q6">
+        <f t="shared" si="2"/>
+        <v>0.92878338278931749</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="3"/>
+        <v>0.84518451845184517</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="4"/>
+        <v>0.21428571428571427</v>
+      </c>
+      <c r="U6">
+        <f t="shared" si="5"/>
+        <v>9.0909090909090912E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1144</v>
       </c>
@@ -694,15 +826,31 @@
       </c>
       <c r="M7"/>
       <c r="N7">
+        <f t="shared" si="1"/>
+        <v>0.94272076372315039</v>
+      </c>
+      <c r="O7">
         <f t="shared" si="0"/>
-        <v>0.94272076372315039</v>
-      </c>
-      <c r="O7">
-        <f t="shared" si="1"/>
         <v>0.69055944055944052</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q7">
+        <f t="shared" si="2"/>
+        <v>0.94477791116446574</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="3"/>
+        <v>0.7083708370837084</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="4"/>
+        <v>0.6</v>
+      </c>
+      <c r="U7">
+        <f t="shared" si="5"/>
+        <v>9.0909090909090912E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1144</v>
       </c>
@@ -741,15 +889,31 @@
       </c>
       <c r="M8"/>
       <c r="N8">
+        <f t="shared" si="1"/>
+        <v>0.95222584147665579</v>
+      </c>
+      <c r="O8">
         <f t="shared" si="0"/>
-        <v>0.95222584147665579</v>
-      </c>
-      <c r="O8">
-        <f t="shared" si="1"/>
         <v>0.76660839160839156</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q8">
+        <f t="shared" si="2"/>
+        <v>0.95618838992332966</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="3"/>
+        <v>0.78577857785778582</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="4"/>
+        <v>0.5</v>
+      </c>
+      <c r="U8">
+        <f t="shared" si="5"/>
+        <v>0.12121212121212122</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>1144</v>
       </c>
@@ -788,15 +952,31 @@
       </c>
       <c r="M9"/>
       <c r="N9">
+        <f t="shared" si="1"/>
+        <v>0.9211538461538461</v>
+      </c>
+      <c r="O9">
         <f t="shared" si="0"/>
-        <v>0.9211538461538461</v>
-      </c>
-      <c r="O9">
-        <f t="shared" si="1"/>
         <v>0.83741258741258739</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q9">
+        <f t="shared" si="2"/>
+        <v>0.93046033300685604</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="3"/>
+        <v>0.85508550855085508</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="4"/>
+        <v>0.42105263157894735</v>
+      </c>
+      <c r="U9">
+        <f t="shared" si="5"/>
+        <v>0.24242424242424243</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>1144</v>
       </c>
@@ -835,15 +1015,31 @@
       </c>
       <c r="M10"/>
       <c r="N10">
-        <f t="shared" ref="N10:N11" si="2">G10/E10</f>
+        <f t="shared" ref="N10:N11" si="6">G10/E10</f>
         <v>0.92144373673036095</v>
       </c>
       <c r="O10">
-        <f t="shared" ref="O10:O11" si="3">G10/A10</f>
+        <f t="shared" ref="O10:O11" si="7">G10/A10</f>
         <v>0.75874125874125875</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q10">
+        <f t="shared" si="2"/>
+        <v>0.93174431202600216</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="3"/>
+        <v>0.77407740774077405</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="4"/>
+        <v>0.5</v>
+      </c>
+      <c r="U10">
+        <f t="shared" si="5"/>
+        <v>0.24242424242424243</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>1144</v>
       </c>
@@ -882,60 +1078,76 @@
       </c>
       <c r="M11"/>
       <c r="N11">
+        <f t="shared" si="6"/>
+        <v>0.93462717058222677</v>
+      </c>
+      <c r="O11">
+        <f t="shared" si="7"/>
+        <v>0.79982517482517479</v>
+      </c>
+      <c r="Q11">
         <f t="shared" si="2"/>
-        <v>0.93462717058222677</v>
-      </c>
-      <c r="O11">
+        <v>0.9391124871001032</v>
+      </c>
+      <c r="R11">
         <f t="shared" si="3"/>
-        <v>0.79982517482517479</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" s="6" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+        <v>0.81908190819081905</v>
+      </c>
+      <c r="T11">
+        <f t="shared" si="4"/>
+        <v>0.5</v>
+      </c>
+      <c r="U11">
+        <f t="shared" si="5"/>
+        <v>0.15151515151515152</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" s="6" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
         <v>14</v>
       </c>
       <c r="B12" s="8">
-        <f t="shared" ref="B12:L12" si="4">AVERAGE(B2:B11)</f>
+        <f t="shared" ref="B12:L12" si="8">AVERAGE(B2:B11)</f>
         <v>1331</v>
       </c>
       <c r="C12" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0.94883546205860259</v>
       </c>
       <c r="D12" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="E12" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>967.2</v>
       </c>
       <c r="F12" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>363.8</v>
       </c>
       <c r="G12" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>899.1</v>
       </c>
       <c r="H12" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>68.099999999999994</v>
       </c>
       <c r="I12" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>5.7</v>
       </c>
       <c r="J12" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>893.4</v>
       </c>
       <c r="K12" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>61.5</v>
       </c>
       <c r="L12" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>6.3</v>
       </c>
       <c r="N12" s="9">
@@ -945,6 +1157,38 @@
       <c r="O12" s="9">
         <f>AVERAGE(O2:O11)</f>
         <v>0.78592657342657346</v>
+      </c>
+      <c r="Q12" s="17">
+        <f t="shared" ref="Q12:R12" si="9">AVERAGE(Q2:Q11)</f>
+        <v>0.93581749767164391</v>
+      </c>
+      <c r="R12" s="17">
+        <f t="shared" si="9"/>
+        <v>0.80414041404140413</v>
+      </c>
+      <c r="S12"/>
+      <c r="T12" s="17">
+        <f t="shared" ref="T12:U12" si="10">AVERAGE(T2:T11)</f>
+        <v>0.50635434740697904</v>
+      </c>
+      <c r="U12" s="17">
+        <f t="shared" si="10"/>
+        <v>0.17272727272727276</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="J13" s="14">
+        <f>J12+K12</f>
+        <v>954.9</v>
+      </c>
+      <c r="L13" s="15">
+        <f>I12+L12</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A16" s="16" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -959,16 +1203,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:O12"/>
+  <dimension ref="A1:U13"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.5546875" style="1" customWidth="1"/>
     <col min="2" max="13" width="12.6640625" style="1"/>
     <col min="14" max="15" width="12.6640625" style="2"/>
-    <col min="16" max="16384" width="12.6640625" style="1"/>
+    <col min="16" max="16" width="12.6640625" style="1"/>
+    <col min="22" max="16384" width="12.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1012,8 +1257,20 @@
       <c r="O1" s="5" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="R1" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1144</v>
       </c>
@@ -1058,8 +1315,24 @@
         <f t="shared" ref="O2:O9" si="1">G2/A2</f>
         <v>0.92307692307692313</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q2">
+        <f>J2/(J2+K2)</f>
+        <v>0.9119718309859155</v>
+      </c>
+      <c r="R2">
+        <f>J2/1111</f>
+        <v>0.93249324932493249</v>
+      </c>
+      <c r="T2">
+        <f>I2/(I2+L2)</f>
+        <v>0.35714285714285715</v>
+      </c>
+      <c r="U2">
+        <f>I2/33</f>
+        <v>0.60606060606060608</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1144</v>
       </c>
@@ -1104,8 +1377,24 @@
         <f t="shared" si="1"/>
         <v>0.96678321678321677</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q3">
+        <f t="shared" ref="Q3:Q11" si="2">J3/(J3+K3)</f>
+        <v>0.89649551752241241</v>
+      </c>
+      <c r="R3">
+        <f>J3/1111</f>
+        <v>0.99009900990099009</v>
+      </c>
+      <c r="T3">
+        <f t="shared" ref="T3:T11" si="3">I3/(I3+L3)</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="U3">
+        <f>I3/33</f>
+        <v>0.18181818181818182</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1144</v>
       </c>
@@ -1150,8 +1439,24 @@
         <f t="shared" si="1"/>
         <v>0.92395104895104896</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q4">
+        <f t="shared" si="2"/>
+        <v>0.89078498293515362</v>
+      </c>
+      <c r="R4">
+        <f>J4/1111</f>
+        <v>0.93969396939693972</v>
+      </c>
+      <c r="T4">
+        <f t="shared" si="3"/>
+        <v>0.37142857142857144</v>
+      </c>
+      <c r="U4">
+        <f t="shared" ref="U3:U11" si="4">I4/33</f>
+        <v>0.39393939393939392</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1144</v>
       </c>
@@ -1196,8 +1501,24 @@
         <f t="shared" si="1"/>
         <v>0.97639860139860135</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q5">
+        <f t="shared" si="2"/>
+        <v>0.91494632535094966</v>
+      </c>
+      <c r="R5">
+        <f t="shared" ref="R3:R11" si="5">J5/1111</f>
+        <v>0.99729972997299732</v>
+      </c>
+      <c r="T5">
+        <f t="shared" si="3"/>
+        <v>0.45</v>
+      </c>
+      <c r="U5">
+        <f t="shared" si="4"/>
+        <v>0.27272727272727271</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1144</v>
       </c>
@@ -1242,8 +1563,24 @@
         <f t="shared" si="1"/>
         <v>0.96416083916083917</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q6">
+        <f t="shared" si="2"/>
+        <v>0.89916666666666667</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="5"/>
+        <v>0.9711971197119712</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="3"/>
+        <v>0.47058823529411764</v>
+      </c>
+      <c r="U6">
+        <f t="shared" si="4"/>
+        <v>0.72727272727272729</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1144</v>
       </c>
@@ -1288,8 +1625,24 @@
         <f t="shared" si="1"/>
         <v>0.92220279720279719</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q7">
+        <f t="shared" si="2"/>
+        <v>0.91277533039647574</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="5"/>
+        <v>0.93249324932493249</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="3"/>
+        <v>0.52777777777777779</v>
+      </c>
+      <c r="U7">
+        <f t="shared" si="4"/>
+        <v>0.5757575757575758</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1144</v>
       </c>
@@ -1334,8 +1687,24 @@
         <f t="shared" si="1"/>
         <v>0.95804195804195802</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q8">
+        <f t="shared" si="2"/>
+        <v>0.91921768707482998</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="5"/>
+        <v>0.97299729972997295</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="3"/>
+        <v>0.40540540540540543</v>
+      </c>
+      <c r="U8">
+        <f t="shared" si="4"/>
+        <v>0.45454545454545453</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>1144</v>
       </c>
@@ -1380,8 +1749,24 @@
         <f t="shared" si="1"/>
         <v>0.96416083916083917</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q9">
+        <f t="shared" si="2"/>
+        <v>0.91109229466553765</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="5"/>
+        <v>0.96849684968496852</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="3"/>
+        <v>0.40909090909090912</v>
+      </c>
+      <c r="U9">
+        <f t="shared" si="4"/>
+        <v>0.81818181818181823</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>1144</v>
       </c>
@@ -1419,15 +1804,31 @@
         <v>14</v>
       </c>
       <c r="N10" s="2">
-        <f t="shared" ref="N10:N11" si="2">G10/E10</f>
+        <f t="shared" ref="N10:N11" si="6">G10/E10</f>
         <v>0.87915652879156525</v>
       </c>
       <c r="O10" s="2">
-        <f t="shared" ref="O10:O11" si="3">G10/A10</f>
+        <f t="shared" ref="O10:O11" si="7">G10/A10</f>
         <v>0.94755244755244761</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q10">
+        <f t="shared" si="2"/>
+        <v>0.88842975206611574</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="5"/>
+        <v>0.96759675967596759</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="3"/>
+        <v>0.39130434782608697</v>
+      </c>
+      <c r="U10">
+        <f t="shared" si="4"/>
+        <v>0.27272727272727271</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>1144</v>
       </c>
@@ -1465,15 +1866,31 @@
         <v>13</v>
       </c>
       <c r="N11" s="2">
+        <f t="shared" si="6"/>
+        <v>0.88392156862745097</v>
+      </c>
+      <c r="O11" s="2">
+        <f t="shared" si="7"/>
+        <v>0.9851398601398601</v>
+      </c>
+      <c r="Q11">
         <f t="shared" si="2"/>
-        <v>0.88392156862745097</v>
-      </c>
-      <c r="O11" s="2">
+        <v>0.89243027888446214</v>
+      </c>
+      <c r="R11">
+        <f t="shared" si="5"/>
+        <v>1.008100810081008</v>
+      </c>
+      <c r="T11">
         <f t="shared" si="3"/>
-        <v>0.9851398601398601</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" s="6" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+        <v>0.35</v>
+      </c>
+      <c r="U11">
+        <f t="shared" si="4"/>
+        <v>0.21212121212121213</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" s="6" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
         <v>14</v>
       </c>
@@ -1521,6 +1938,33 @@
       <c r="O12" s="9">
         <f>AVERAGE(O2:O11)</f>
         <v>0.95314685314685332</v>
+      </c>
+      <c r="Q12" s="17">
+        <f t="shared" ref="Q12:R12" si="8">AVERAGE(Q2:Q11)</f>
+        <v>0.9037310666548517</v>
+      </c>
+      <c r="R12" s="17">
+        <f t="shared" si="8"/>
+        <v>0.96804680468046789</v>
+      </c>
+      <c r="S12"/>
+      <c r="T12" s="17">
+        <f t="shared" ref="T12:U12" si="9">AVERAGE(T2:T11)</f>
+        <v>0.40660714372990581</v>
+      </c>
+      <c r="U12" s="17">
+        <f t="shared" si="9"/>
+        <v>0.45151515151515148</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="J13" s="15">
+        <f>J12+K12</f>
+        <v>1190.3</v>
+      </c>
+      <c r="L13" s="15">
+        <f>I12+L12</f>
+        <v>36.200000000000003</v>
       </c>
     </row>
   </sheetData>
@@ -1535,16 +1979,17 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:O102"/>
+  <dimension ref="A1:U102"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.5546875" style="1" customWidth="1"/>
     <col min="2" max="13" width="12.6640625" style="1"/>
     <col min="15" max="15" width="12.6640625" style="2"/>
-    <col min="16" max="16384" width="12.6640625" style="1"/>
+    <col min="16" max="16" width="12.6640625" style="1"/>
+    <col min="22" max="16384" width="12.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -1588,8 +2033,20 @@
       <c r="O1" s="3" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="R1" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1144</v>
       </c>
@@ -1634,8 +2091,24 @@
         <f t="shared" ref="O2:O9" si="1">G2/A2</f>
         <v>0.97639860139860135</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q2">
+        <f>J2/(J2+K2)</f>
+        <v>0.89089417555373251</v>
+      </c>
+      <c r="R2">
+        <f>J2/1111</f>
+        <v>0.9774977497749775</v>
+      </c>
+      <c r="T2">
+        <f>I2/(I2+L2)</f>
+        <v>0.29807692307692307</v>
+      </c>
+      <c r="U2">
+        <f>I2/33</f>
+        <v>0.93939393939393945</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1144</v>
       </c>
@@ -1680,8 +2153,24 @@
         <f t="shared" si="1"/>
         <v>0.99912587412587417</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q3">
+        <f t="shared" ref="Q3:Q11" si="2">J3/(J3+K3)</f>
+        <v>0.88766692851531814</v>
+      </c>
+      <c r="R3">
+        <f t="shared" ref="R3:R11" si="3">J3/1111</f>
+        <v>1.0171017101710171</v>
+      </c>
+      <c r="T3">
+        <f t="shared" ref="T3:T11" si="4">I3/(I3+L3)</f>
+        <v>0.43333333333333335</v>
+      </c>
+      <c r="U3">
+        <f>I3/33</f>
+        <v>0.39393939393939392</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1144</v>
       </c>
@@ -1726,8 +2215,24 @@
         <f t="shared" si="1"/>
         <v>0.97027972027972031</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q4">
+        <f t="shared" si="2"/>
+        <v>0.87844408427876819</v>
+      </c>
+      <c r="R4">
+        <f t="shared" si="3"/>
+        <v>0.97569756975697575</v>
+      </c>
+      <c r="T4">
+        <f t="shared" si="4"/>
+        <v>0.41935483870967744</v>
+      </c>
+      <c r="U4">
+        <f t="shared" ref="U3:U11" si="5">I4/33</f>
+        <v>0.78787878787878785</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1144</v>
       </c>
@@ -1772,8 +2277,24 @@
         <f t="shared" si="1"/>
         <v>1.0131118881118881</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q5">
+        <f t="shared" si="2"/>
+        <v>0.90634920634920635</v>
+      </c>
+      <c r="R5">
+        <f t="shared" si="3"/>
+        <v>1.0279027902790279</v>
+      </c>
+      <c r="T5">
+        <f t="shared" si="4"/>
+        <v>0.38636363636363635</v>
+      </c>
+      <c r="U5">
+        <f t="shared" si="5"/>
+        <v>0.51515151515151514</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1144</v>
       </c>
@@ -1818,8 +2339,24 @@
         <f t="shared" si="1"/>
         <v>0.97202797202797198</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q6">
+        <f t="shared" si="2"/>
+        <v>0.89752066115702478</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="3"/>
+        <v>0.9774977497749775</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="4"/>
+        <v>0.42622950819672129</v>
+      </c>
+      <c r="U6">
+        <f t="shared" si="5"/>
+        <v>0.78787878787878785</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1144</v>
       </c>
@@ -1864,8 +2401,24 @@
         <f t="shared" si="1"/>
         <v>1.0052447552447552</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q7">
+        <f t="shared" si="2"/>
+        <v>0.89967637540453071</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="3"/>
+        <v>1.0009000900090008</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="4"/>
+        <v>0.40860215053763443</v>
+      </c>
+      <c r="U7">
+        <f t="shared" si="5"/>
+        <v>1.1515151515151516</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1144</v>
       </c>
@@ -1910,8 +2463,24 @@
         <f t="shared" si="1"/>
         <v>0.98863636363636365</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q8">
+        <f t="shared" si="2"/>
+        <v>0.91133004926108374</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="3"/>
+        <v>0.99909990999099907</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="4"/>
+        <v>0.3559322033898305</v>
+      </c>
+      <c r="U8">
+        <f t="shared" si="5"/>
+        <v>0.63636363636363635</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>1144</v>
       </c>
@@ -1956,8 +2525,24 @@
         <f t="shared" si="1"/>
         <v>0.97290209790209792</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q9">
+        <f t="shared" si="2"/>
+        <v>0.90848026868178</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="3"/>
+        <v>0.97389738973897388</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="4"/>
+        <v>0.38271604938271603</v>
+      </c>
+      <c r="U9">
+        <f t="shared" si="5"/>
+        <v>0.93939393939393945</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>1144</v>
       </c>
@@ -2002,8 +2587,24 @@
         <f>G10/A10</f>
         <v>0.96853146853146854</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q10">
+        <f t="shared" si="2"/>
+        <v>0.88387096774193552</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="3"/>
+        <v>0.98649864986498648</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="4"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="U10">
+        <f t="shared" si="5"/>
+        <v>0.36363636363636365</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>1144</v>
       </c>
@@ -2048,8 +2649,24 @@
         <f>G11/A11</f>
         <v>0.97639860139860135</v>
       </c>
-    </row>
-    <row r="12" spans="1:15" s="6" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="Q11">
+        <f t="shared" si="2"/>
+        <v>0.8915365653245686</v>
+      </c>
+      <c r="R11">
+        <f t="shared" si="3"/>
+        <v>0.97659765976597657</v>
+      </c>
+      <c r="T11">
+        <f t="shared" si="4"/>
+        <v>0.30188679245283018</v>
+      </c>
+      <c r="U11">
+        <f t="shared" si="5"/>
+        <v>0.96969696969696972</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" s="6" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="11">
         <v>1331</v>
       </c>
@@ -2098,97 +2715,663 @@
         <f>AVERAGE(O2:O11)</f>
         <v>0.98426573426573416</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="1:15" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="15" spans="1:15" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="16" spans="1:15" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="17" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="18" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="19" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="20" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="22" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="23" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="24" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="25" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="26" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="27" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="28" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="29" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="30" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="31" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="32" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="33" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="34" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="35" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="36" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="37" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="38" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="39" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="40" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="41" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="42" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="43" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="44" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="45" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="46" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="47" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="48" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="49" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="50" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="51" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="52" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="53" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="54" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="55" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="56" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="57" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="58" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="59" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="60" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="61" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="62" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="63" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="64" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="65" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="66" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="67" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="68" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="69" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="70" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="71" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="72" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="73" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="74" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="75" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="76" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="77" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="78" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="79" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="80" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="81" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="82" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="83" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="84" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="85" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="86" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="87" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="88" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="89" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="90" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="91" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="92" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="93" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="94" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="95" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="96" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="97" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="98" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="99" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="100" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="101" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="102" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
+      <c r="Q12" s="17">
+        <f t="shared" ref="Q12:R12" si="6">AVERAGE(Q2:Q11)</f>
+        <v>0.8955769282267948</v>
+      </c>
+      <c r="R12" s="17">
+        <f t="shared" si="6"/>
+        <v>0.99126912691269131</v>
+      </c>
+      <c r="S12"/>
+      <c r="T12" s="17">
+        <f t="shared" ref="T12:U12" si="7">AVERAGE(T2:T11)</f>
+        <v>0.37458287687766362</v>
+      </c>
+      <c r="U12" s="17">
+        <f t="shared" si="7"/>
+        <v>0.74848484848484842</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J13" s="15">
+        <f>J12+K12</f>
+        <v>1229.8</v>
+      </c>
+      <c r="K13" s="1"/>
+      <c r="L13" s="15">
+        <f>I12+L12</f>
+        <v>67.599999999999994</v>
+      </c>
+      <c r="Q13"/>
+      <c r="R13"/>
+      <c r="S13"/>
+      <c r="T13"/>
+      <c r="U13"/>
+    </row>
+    <row r="14" spans="1:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q14"/>
+      <c r="R14"/>
+      <c r="S14"/>
+      <c r="T14"/>
+      <c r="U14"/>
+    </row>
+    <row r="15" spans="1:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q15"/>
+      <c r="R15"/>
+      <c r="S15"/>
+      <c r="T15"/>
+      <c r="U15"/>
+    </row>
+    <row r="16" spans="1:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q16"/>
+      <c r="R16"/>
+      <c r="S16"/>
+      <c r="T16"/>
+      <c r="U16"/>
+    </row>
+    <row r="17" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q17"/>
+      <c r="R17"/>
+      <c r="S17"/>
+      <c r="T17"/>
+      <c r="U17"/>
+    </row>
+    <row r="18" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q18"/>
+      <c r="R18"/>
+      <c r="S18"/>
+      <c r="T18"/>
+      <c r="U18"/>
+    </row>
+    <row r="19" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q19"/>
+      <c r="R19"/>
+      <c r="S19"/>
+      <c r="T19"/>
+      <c r="U19"/>
+    </row>
+    <row r="20" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q20"/>
+      <c r="R20"/>
+      <c r="S20"/>
+      <c r="T20"/>
+      <c r="U20"/>
+    </row>
+    <row r="21" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q21"/>
+      <c r="R21"/>
+      <c r="S21"/>
+      <c r="T21"/>
+      <c r="U21"/>
+    </row>
+    <row r="22" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q22"/>
+      <c r="R22"/>
+      <c r="S22"/>
+      <c r="T22"/>
+      <c r="U22"/>
+    </row>
+    <row r="23" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q23"/>
+      <c r="R23"/>
+      <c r="S23"/>
+      <c r="T23"/>
+      <c r="U23"/>
+    </row>
+    <row r="24" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q24"/>
+      <c r="R24"/>
+      <c r="S24"/>
+      <c r="T24"/>
+      <c r="U24"/>
+    </row>
+    <row r="25" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q25"/>
+      <c r="R25"/>
+      <c r="S25"/>
+      <c r="T25"/>
+      <c r="U25"/>
+    </row>
+    <row r="26" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q26"/>
+      <c r="R26"/>
+      <c r="S26"/>
+      <c r="T26"/>
+      <c r="U26"/>
+    </row>
+    <row r="27" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q27"/>
+      <c r="R27"/>
+      <c r="S27"/>
+      <c r="T27"/>
+      <c r="U27"/>
+    </row>
+    <row r="28" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q28"/>
+      <c r="R28"/>
+      <c r="S28"/>
+      <c r="T28"/>
+      <c r="U28"/>
+    </row>
+    <row r="29" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q29"/>
+      <c r="R29"/>
+      <c r="S29"/>
+      <c r="T29"/>
+      <c r="U29"/>
+    </row>
+    <row r="30" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q30"/>
+      <c r="R30"/>
+      <c r="S30"/>
+      <c r="T30"/>
+      <c r="U30"/>
+    </row>
+    <row r="31" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q31"/>
+      <c r="R31"/>
+      <c r="S31"/>
+      <c r="T31"/>
+      <c r="U31"/>
+    </row>
+    <row r="32" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q32"/>
+      <c r="R32"/>
+      <c r="S32"/>
+      <c r="T32"/>
+      <c r="U32"/>
+    </row>
+    <row r="33" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q33"/>
+      <c r="R33"/>
+      <c r="S33"/>
+      <c r="T33"/>
+      <c r="U33"/>
+    </row>
+    <row r="34" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q34"/>
+      <c r="R34"/>
+      <c r="S34"/>
+      <c r="T34"/>
+      <c r="U34"/>
+    </row>
+    <row r="35" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q35"/>
+      <c r="R35"/>
+      <c r="S35"/>
+      <c r="T35"/>
+      <c r="U35"/>
+    </row>
+    <row r="36" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q36"/>
+      <c r="R36"/>
+      <c r="S36"/>
+      <c r="T36"/>
+      <c r="U36"/>
+    </row>
+    <row r="37" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q37"/>
+      <c r="R37"/>
+      <c r="S37"/>
+      <c r="T37"/>
+      <c r="U37"/>
+    </row>
+    <row r="38" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q38"/>
+      <c r="R38"/>
+      <c r="S38"/>
+      <c r="T38"/>
+      <c r="U38"/>
+    </row>
+    <row r="39" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q39"/>
+      <c r="R39"/>
+      <c r="S39"/>
+      <c r="T39"/>
+      <c r="U39"/>
+    </row>
+    <row r="40" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q40"/>
+      <c r="R40"/>
+      <c r="S40"/>
+      <c r="T40"/>
+      <c r="U40"/>
+    </row>
+    <row r="41" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q41"/>
+      <c r="R41"/>
+      <c r="S41"/>
+      <c r="T41"/>
+      <c r="U41"/>
+    </row>
+    <row r="42" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q42"/>
+      <c r="R42"/>
+      <c r="S42"/>
+      <c r="T42"/>
+      <c r="U42"/>
+    </row>
+    <row r="43" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q43"/>
+      <c r="R43"/>
+      <c r="S43"/>
+      <c r="T43"/>
+      <c r="U43"/>
+    </row>
+    <row r="44" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q44"/>
+      <c r="R44"/>
+      <c r="S44"/>
+      <c r="T44"/>
+      <c r="U44"/>
+    </row>
+    <row r="45" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q45"/>
+      <c r="R45"/>
+      <c r="S45"/>
+      <c r="T45"/>
+      <c r="U45"/>
+    </row>
+    <row r="46" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q46"/>
+      <c r="R46"/>
+      <c r="S46"/>
+      <c r="T46"/>
+      <c r="U46"/>
+    </row>
+    <row r="47" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q47"/>
+      <c r="R47"/>
+      <c r="S47"/>
+      <c r="T47"/>
+      <c r="U47"/>
+    </row>
+    <row r="48" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q48"/>
+      <c r="R48"/>
+      <c r="S48"/>
+      <c r="T48"/>
+      <c r="U48"/>
+    </row>
+    <row r="49" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q49"/>
+      <c r="R49"/>
+      <c r="S49"/>
+      <c r="T49"/>
+      <c r="U49"/>
+    </row>
+    <row r="50" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q50"/>
+      <c r="R50"/>
+      <c r="S50"/>
+      <c r="T50"/>
+      <c r="U50"/>
+    </row>
+    <row r="51" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q51"/>
+      <c r="R51"/>
+      <c r="S51"/>
+      <c r="T51"/>
+      <c r="U51"/>
+    </row>
+    <row r="52" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q52"/>
+      <c r="R52"/>
+      <c r="S52"/>
+      <c r="T52"/>
+      <c r="U52"/>
+    </row>
+    <row r="53" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q53"/>
+      <c r="R53"/>
+      <c r="S53"/>
+      <c r="T53"/>
+      <c r="U53"/>
+    </row>
+    <row r="54" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q54"/>
+      <c r="R54"/>
+      <c r="S54"/>
+      <c r="T54"/>
+      <c r="U54"/>
+    </row>
+    <row r="55" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q55"/>
+      <c r="R55"/>
+      <c r="S55"/>
+      <c r="T55"/>
+      <c r="U55"/>
+    </row>
+    <row r="56" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q56"/>
+      <c r="R56"/>
+      <c r="S56"/>
+      <c r="T56"/>
+      <c r="U56"/>
+    </row>
+    <row r="57" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q57"/>
+      <c r="R57"/>
+      <c r="S57"/>
+      <c r="T57"/>
+      <c r="U57"/>
+    </row>
+    <row r="58" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q58"/>
+      <c r="R58"/>
+      <c r="S58"/>
+      <c r="T58"/>
+      <c r="U58"/>
+    </row>
+    <row r="59" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q59"/>
+      <c r="R59"/>
+      <c r="S59"/>
+      <c r="T59"/>
+      <c r="U59"/>
+    </row>
+    <row r="60" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q60"/>
+      <c r="R60"/>
+      <c r="S60"/>
+      <c r="T60"/>
+      <c r="U60"/>
+    </row>
+    <row r="61" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q61"/>
+      <c r="R61"/>
+      <c r="S61"/>
+      <c r="T61"/>
+      <c r="U61"/>
+    </row>
+    <row r="62" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q62"/>
+      <c r="R62"/>
+      <c r="S62"/>
+      <c r="T62"/>
+      <c r="U62"/>
+    </row>
+    <row r="63" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q63"/>
+      <c r="R63"/>
+      <c r="S63"/>
+      <c r="T63"/>
+      <c r="U63"/>
+    </row>
+    <row r="64" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q64"/>
+      <c r="R64"/>
+      <c r="S64"/>
+      <c r="T64"/>
+      <c r="U64"/>
+    </row>
+    <row r="65" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q65"/>
+      <c r="R65"/>
+      <c r="S65"/>
+      <c r="T65"/>
+      <c r="U65"/>
+    </row>
+    <row r="66" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q66"/>
+      <c r="R66"/>
+      <c r="S66"/>
+      <c r="T66"/>
+      <c r="U66"/>
+    </row>
+    <row r="67" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q67"/>
+      <c r="R67"/>
+      <c r="S67"/>
+      <c r="T67"/>
+      <c r="U67"/>
+    </row>
+    <row r="68" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q68"/>
+      <c r="R68"/>
+      <c r="S68"/>
+      <c r="T68"/>
+      <c r="U68"/>
+    </row>
+    <row r="69" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q69"/>
+      <c r="R69"/>
+      <c r="S69"/>
+      <c r="T69"/>
+      <c r="U69"/>
+    </row>
+    <row r="70" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q70"/>
+      <c r="R70"/>
+      <c r="S70"/>
+      <c r="T70"/>
+      <c r="U70"/>
+    </row>
+    <row r="71" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q71"/>
+      <c r="R71"/>
+      <c r="S71"/>
+      <c r="T71"/>
+      <c r="U71"/>
+    </row>
+    <row r="72" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q72"/>
+      <c r="R72"/>
+      <c r="S72"/>
+      <c r="T72"/>
+      <c r="U72"/>
+    </row>
+    <row r="73" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q73"/>
+      <c r="R73"/>
+      <c r="S73"/>
+      <c r="T73"/>
+      <c r="U73"/>
+    </row>
+    <row r="74" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q74"/>
+      <c r="R74"/>
+      <c r="S74"/>
+      <c r="T74"/>
+      <c r="U74"/>
+    </row>
+    <row r="75" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q75"/>
+      <c r="R75"/>
+      <c r="S75"/>
+      <c r="T75"/>
+      <c r="U75"/>
+    </row>
+    <row r="76" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q76"/>
+      <c r="R76"/>
+      <c r="S76"/>
+      <c r="T76"/>
+      <c r="U76"/>
+    </row>
+    <row r="77" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q77"/>
+      <c r="R77"/>
+      <c r="S77"/>
+      <c r="T77"/>
+      <c r="U77"/>
+    </row>
+    <row r="78" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q78"/>
+      <c r="R78"/>
+      <c r="S78"/>
+      <c r="T78"/>
+      <c r="U78"/>
+    </row>
+    <row r="79" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q79"/>
+      <c r="R79"/>
+      <c r="S79"/>
+      <c r="T79"/>
+      <c r="U79"/>
+    </row>
+    <row r="80" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q80"/>
+      <c r="R80"/>
+      <c r="S80"/>
+      <c r="T80"/>
+      <c r="U80"/>
+    </row>
+    <row r="81" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q81"/>
+      <c r="R81"/>
+      <c r="S81"/>
+      <c r="T81"/>
+      <c r="U81"/>
+    </row>
+    <row r="82" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q82"/>
+      <c r="R82"/>
+      <c r="S82"/>
+      <c r="T82"/>
+      <c r="U82"/>
+    </row>
+    <row r="83" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q83"/>
+      <c r="R83"/>
+      <c r="S83"/>
+      <c r="T83"/>
+      <c r="U83"/>
+    </row>
+    <row r="84" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q84"/>
+      <c r="R84"/>
+      <c r="S84"/>
+      <c r="T84"/>
+      <c r="U84"/>
+    </row>
+    <row r="85" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q85"/>
+      <c r="R85"/>
+      <c r="S85"/>
+      <c r="T85"/>
+      <c r="U85"/>
+    </row>
+    <row r="86" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q86"/>
+      <c r="R86"/>
+      <c r="S86"/>
+      <c r="T86"/>
+      <c r="U86"/>
+    </row>
+    <row r="87" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q87"/>
+      <c r="R87"/>
+      <c r="S87"/>
+      <c r="T87"/>
+      <c r="U87"/>
+    </row>
+    <row r="88" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q88"/>
+      <c r="R88"/>
+      <c r="S88"/>
+      <c r="T88"/>
+      <c r="U88"/>
+    </row>
+    <row r="89" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q89"/>
+      <c r="R89"/>
+      <c r="S89"/>
+      <c r="T89"/>
+      <c r="U89"/>
+    </row>
+    <row r="90" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q90"/>
+      <c r="R90"/>
+      <c r="S90"/>
+      <c r="T90"/>
+      <c r="U90"/>
+    </row>
+    <row r="91" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q91"/>
+      <c r="R91"/>
+      <c r="S91"/>
+      <c r="T91"/>
+      <c r="U91"/>
+    </row>
+    <row r="92" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q92"/>
+      <c r="R92"/>
+      <c r="S92"/>
+      <c r="T92"/>
+      <c r="U92"/>
+    </row>
+    <row r="93" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q93"/>
+      <c r="R93"/>
+      <c r="S93"/>
+      <c r="T93"/>
+      <c r="U93"/>
+    </row>
+    <row r="94" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q94"/>
+      <c r="R94"/>
+      <c r="S94"/>
+      <c r="T94"/>
+      <c r="U94"/>
+    </row>
+    <row r="95" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q95"/>
+      <c r="R95"/>
+      <c r="S95"/>
+      <c r="T95"/>
+      <c r="U95"/>
+    </row>
+    <row r="96" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q96"/>
+      <c r="R96"/>
+      <c r="S96"/>
+      <c r="T96"/>
+      <c r="U96"/>
+    </row>
+    <row r="97" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q97"/>
+      <c r="R97"/>
+      <c r="S97"/>
+      <c r="T97"/>
+      <c r="U97"/>
+    </row>
+    <row r="98" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q98"/>
+      <c r="R98"/>
+      <c r="S98"/>
+      <c r="T98"/>
+      <c r="U98"/>
+    </row>
+    <row r="99" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q99"/>
+      <c r="R99"/>
+      <c r="S99"/>
+      <c r="T99"/>
+      <c r="U99"/>
+    </row>
+    <row r="100" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q100"/>
+      <c r="R100"/>
+      <c r="S100"/>
+      <c r="T100"/>
+      <c r="U100"/>
+    </row>
+    <row r="101" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q101"/>
+      <c r="R101"/>
+      <c r="S101"/>
+      <c r="T101"/>
+      <c r="U101"/>
+    </row>
+    <row r="102" spans="17:21" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q102"/>
+      <c r="R102"/>
+      <c r="S102"/>
+      <c r="T102"/>
+      <c r="U102"/>
+    </row>
   </sheetData>
   <pageMargins left="0.78750000000000009" right="0.78750000000000009" top="1.0249999999999997" bottom="1.0249999999999997" header="0.78750000000000009" footer="0.78750000000000009"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -2201,16 +3384,17 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:O12"/>
+  <dimension ref="A1:U15"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.33203125" style="2" customWidth="1"/>
     <col min="2" max="12" width="12.6640625" style="1"/>
     <col min="13" max="13" width="12.6640625" style="2"/>
-    <col min="14" max="16384" width="12.6640625" style="1"/>
+    <col min="14" max="16" width="12.6640625" style="1"/>
+    <col min="22" max="16384" width="12.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -2254,8 +3438,20 @@
       <c r="O1" s="5" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="R1" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>2355</v>
       </c>
@@ -2300,8 +3496,24 @@
         <f t="shared" ref="O2:O9" si="1">G2/A2</f>
         <v>0.91337579617834397</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q2">
+        <f>J2/(J2+K2)</f>
+        <v>0.95086321381142103</v>
+      </c>
+      <c r="R2">
+        <f>J2/2326</f>
+        <v>0.92347377472055026</v>
+      </c>
+      <c r="T2">
+        <f>I2/(I2+L2)</f>
+        <v>0.3</v>
+      </c>
+      <c r="U2">
+        <f>I2/29</f>
+        <v>0.10344827586206896</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>2355</v>
       </c>
@@ -2346,8 +3558,24 @@
         <f t="shared" si="1"/>
         <v>0.95711252653927814</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q3">
+        <f t="shared" ref="Q3:Q11" si="2">J3/(J3+K3)</f>
+        <v>0.94300083822296732</v>
+      </c>
+      <c r="R3">
+        <f t="shared" ref="R3:R11" si="3">J3/2326</f>
+        <v>0.96732588134135855</v>
+      </c>
+      <c r="T3">
+        <f t="shared" ref="T3:T11" si="4">I3/(I3+L3)</f>
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="U3">
+        <f t="shared" ref="U3:U11" si="5">I3/29</f>
+        <v>0.13793103448275862</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>2355</v>
       </c>
@@ -2392,8 +3620,24 @@
         <f t="shared" si="1"/>
         <v>0.95074309978768579</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q4">
+        <f t="shared" si="2"/>
+        <v>0.9516474112109542</v>
+      </c>
+      <c r="R4">
+        <f t="shared" si="3"/>
+        <v>0.9561478933791917</v>
+      </c>
+      <c r="T4">
+        <f t="shared" si="4"/>
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="U4">
+        <f t="shared" si="5"/>
+        <v>0.51724137931034486</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>2355</v>
       </c>
@@ -2438,8 +3682,24 @@
         <f t="shared" si="1"/>
         <v>0.92823779193205946</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q5">
+        <f t="shared" si="2"/>
+        <v>0.96235606731620904</v>
+      </c>
+      <c r="R5">
+        <f t="shared" si="3"/>
+        <v>0.93422184006878761</v>
+      </c>
+      <c r="T5">
+        <f t="shared" si="4"/>
+        <v>0.56521739130434778</v>
+      </c>
+      <c r="U5">
+        <f t="shared" si="5"/>
+        <v>0.44827586206896552</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>2355</v>
       </c>
@@ -2484,8 +3744,24 @@
         <f t="shared" si="1"/>
         <v>0.89936305732484079</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q6">
+        <f t="shared" si="2"/>
+        <v>0.95693563009972804</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="3"/>
+        <v>0.90756663800515902</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="4"/>
+        <v>0.46666666666666667</v>
+      </c>
+      <c r="U6">
+        <f t="shared" si="5"/>
+        <v>0.2413793103448276</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>2355</v>
       </c>
@@ -2530,8 +3806,24 @@
         <f t="shared" si="1"/>
         <v>0.89002123142250533</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q7">
+        <f t="shared" si="2"/>
+        <v>0.95510765002290421</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="3"/>
+        <v>0.89638865004299229</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="4"/>
+        <v>0.44</v>
+      </c>
+      <c r="U7">
+        <f t="shared" si="5"/>
+        <v>0.37931034482758619</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>2355</v>
       </c>
@@ -2576,8 +3868,24 @@
         <f t="shared" si="1"/>
         <v>0.93842887473460723</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q8">
+        <f t="shared" si="2"/>
+        <v>0.93974358974358974</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="3"/>
+        <v>0.94539982803095446</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="4"/>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="U8">
+        <f t="shared" si="5"/>
+        <v>0.37931034482758619</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>2355</v>
       </c>
@@ -2622,8 +3930,24 @@
         <f t="shared" si="1"/>
         <v>0.88874734607218686</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q9">
+        <f t="shared" si="2"/>
+        <v>0.95640201927489676</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="3"/>
+        <v>0.8959587274290628</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="4"/>
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="U9">
+        <f t="shared" si="5"/>
+        <v>0.31034482758620691</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>2355</v>
       </c>
@@ -2661,15 +3985,31 @@
         <v>43</v>
       </c>
       <c r="N10" s="2">
-        <f t="shared" ref="N10" si="2">G10/E10</f>
+        <f t="shared" ref="N10" si="6">G10/E10</f>
         <v>0.94266055045871555</v>
       </c>
       <c r="O10" s="2">
         <f>G10/A10</f>
         <v>0.87261146496815289</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q10">
+        <f t="shared" si="2"/>
+        <v>0.96135721017907638</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="3"/>
+        <v>0.87704213241616513</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="4"/>
+        <v>0.25862068965517243</v>
+      </c>
+      <c r="U10">
+        <f t="shared" si="5"/>
+        <v>0.51724137931034486</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>2355</v>
       </c>
@@ -2714,8 +4054,24 @@
         <f>G11/A11</f>
         <v>0.89002123142250533</v>
       </c>
-    </row>
-    <row r="12" spans="1:15" s="6" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="Q11">
+        <f t="shared" si="2"/>
+        <v>0.95464956481905638</v>
+      </c>
+      <c r="R11">
+        <f t="shared" si="3"/>
+        <v>0.8959587274290628</v>
+      </c>
+      <c r="T11">
+        <f t="shared" si="4"/>
+        <v>0.4</v>
+      </c>
+      <c r="U11">
+        <f t="shared" si="5"/>
+        <v>0.34482758620689657</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" s="6" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B12" s="11">
         <v>2571</v>
       </c>
@@ -2761,6 +4117,38 @@
       <c r="O12" s="9">
         <f>AVERAGE(O2:O11)</f>
         <v>0.91286624203821665</v>
+      </c>
+      <c r="Q12" s="17">
+        <f t="shared" ref="Q12:R12" si="7">AVERAGE(Q2:Q11)</f>
+        <v>0.95320631947008039</v>
+      </c>
+      <c r="R12" s="17">
+        <f t="shared" si="7"/>
+        <v>0.91994840928632837</v>
+      </c>
+      <c r="S12"/>
+      <c r="T12" s="17">
+        <f t="shared" ref="T12:U12" si="8">AVERAGE(T2:T11)</f>
+        <v>0.46233618904833296</v>
+      </c>
+      <c r="U12" s="17">
+        <f t="shared" si="8"/>
+        <v>0.33793103448275863</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="J13" s="14">
+        <f>J12+K12</f>
+        <v>2245.3000000000002</v>
+      </c>
+      <c r="L13" s="15">
+        <f>I12+L12</f>
+        <v>23.200000000000003</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="H15" s="16" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -2775,14 +4163,15 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:O12"/>
+  <dimension ref="A1:U13"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.33203125" style="1" customWidth="1"/>
-    <col min="2" max="16384" width="12.6640625" style="1"/>
+    <col min="2" max="16" width="12.6640625" style="1"/>
+    <col min="22" max="16384" width="12.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -2826,8 +4215,20 @@
       <c r="O1" s="5" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="R1" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>2355</v>
       </c>
@@ -2872,8 +4273,24 @@
         <f t="shared" ref="O2:O9" si="1">G2/A2</f>
         <v>0.98683651804670913</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q2">
+        <f>J2/(J2+K2)</f>
+        <v>0.94067452255180817</v>
+      </c>
+      <c r="R2">
+        <f>J2/2326</f>
+        <v>0.99527085124677561</v>
+      </c>
+      <c r="T2">
+        <f>I2/(I2+L2)</f>
+        <v>0.25</v>
+      </c>
+      <c r="U2">
+        <f>I2/29</f>
+        <v>0.31034482758620691</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>2355</v>
       </c>
@@ -2918,8 +4335,24 @@
         <f t="shared" si="1"/>
         <v>0.9881104033970276</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q3">
+        <f t="shared" ref="Q3:Q11" si="2">J3/(J3+K3)</f>
+        <v>0.93699515347334406</v>
+      </c>
+      <c r="R3">
+        <f t="shared" ref="R3:R11" si="3">J3/2326</f>
+        <v>0.99742046431642306</v>
+      </c>
+      <c r="T3">
+        <f t="shared" ref="T3:T11" si="4">I3/(I3+L3)</f>
+        <v>0.36842105263157893</v>
+      </c>
+      <c r="U3">
+        <f t="shared" ref="U3:U11" si="5">I3/29</f>
+        <v>0.2413793103448276</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>2355</v>
       </c>
@@ -2964,8 +4397,24 @@
         <f t="shared" si="1"/>
         <v>0.98853503184713376</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q4">
+        <f t="shared" si="2"/>
+        <v>0.94555873925501432</v>
+      </c>
+      <c r="R4">
+        <f t="shared" si="3"/>
+        <v>0.99312123817712816</v>
+      </c>
+      <c r="T4">
+        <f t="shared" si="4"/>
+        <v>0.29508196721311475</v>
+      </c>
+      <c r="U4">
+        <f t="shared" si="5"/>
+        <v>0.62068965517241381</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>2355</v>
       </c>
@@ -3010,8 +4459,24 @@
         <f t="shared" si="1"/>
         <v>0.99363057324840764</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q5">
+        <f t="shared" si="2"/>
+        <v>0.95004095004095002</v>
+      </c>
+      <c r="R5">
+        <f t="shared" si="3"/>
+        <v>0.99742046431642306</v>
+      </c>
+      <c r="T5">
+        <f t="shared" si="4"/>
+        <v>0.35087719298245612</v>
+      </c>
+      <c r="U5">
+        <f t="shared" si="5"/>
+        <v>0.68965517241379315</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>2355</v>
       </c>
@@ -3056,8 +4521,24 @@
         <f t="shared" si="1"/>
         <v>0.99872611464968153</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q6">
+        <f t="shared" si="2"/>
+        <v>0.93702366626554356</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="3"/>
+        <v>1.0042992261392949</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="4"/>
+        <v>0.30188679245283018</v>
+      </c>
+      <c r="U6">
+        <f t="shared" si="5"/>
+        <v>0.55172413793103448</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>2355</v>
       </c>
@@ -3102,8 +4583,24 @@
         <f t="shared" si="1"/>
         <v>0.98980891719745223</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q7">
+        <f t="shared" si="2"/>
+        <v>0.94214197784160858</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="3"/>
+        <v>0.98710232158211519</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="4"/>
+        <v>0.29411764705882354</v>
+      </c>
+      <c r="U7">
+        <f t="shared" si="5"/>
+        <v>1.2068965517241379</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>2355</v>
       </c>
@@ -3148,8 +4645,24 @@
         <f t="shared" si="1"/>
         <v>0.96475583864118897</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q8">
+        <f t="shared" si="2"/>
+        <v>0.93773349937733497</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="3"/>
+        <v>0.97119518486672396</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="4"/>
+        <v>0.39393939393939392</v>
+      </c>
+      <c r="U8">
+        <f t="shared" si="5"/>
+        <v>0.44827586206896552</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>2355</v>
       </c>
@@ -3194,8 +4707,24 @@
         <f t="shared" si="1"/>
         <v>0.97579617834394905</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q9">
+        <f t="shared" si="2"/>
+        <v>0.94269102990033227</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="3"/>
+        <v>0.97592433361994846</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="4"/>
+        <v>0.4375</v>
+      </c>
+      <c r="U9">
+        <f t="shared" si="5"/>
+        <v>0.96551724137931039</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>2355</v>
       </c>
@@ -3240,8 +4769,24 @@
         <f>G10/A10</f>
         <v>0.97154989384288748</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q10">
+        <f t="shared" si="2"/>
+        <v>0.94451450189155106</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="3"/>
+        <v>0.96603611349957008</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="4"/>
+        <v>0.25465838509316768</v>
+      </c>
+      <c r="U10">
+        <f t="shared" si="5"/>
+        <v>1.4137931034482758</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>2355</v>
       </c>
@@ -3286,8 +4831,24 @@
         <f>G11/A11</f>
         <v>0.99363057324840764</v>
       </c>
-    </row>
-    <row r="12" spans="1:15" s="6" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="Q11">
+        <f t="shared" si="2"/>
+        <v>0.95040983606557372</v>
+      </c>
+      <c r="R11">
+        <f t="shared" si="3"/>
+        <v>0.99699054170249357</v>
+      </c>
+      <c r="T11">
+        <f t="shared" si="4"/>
+        <v>0.3559322033898305</v>
+      </c>
+      <c r="U11">
+        <f t="shared" si="5"/>
+        <v>0.72413793103448276</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" s="6" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="11">
         <v>2571</v>
       </c>
@@ -3335,6 +4896,33 @@
       <c r="O12" s="9">
         <f>AVERAGE(O2:O11)</f>
         <v>0.98513800424628462</v>
+      </c>
+      <c r="Q12" s="17">
+        <f t="shared" ref="Q12:R12" si="6">AVERAGE(Q2:Q11)</f>
+        <v>0.94277838766630606</v>
+      </c>
+      <c r="R12" s="17">
+        <f t="shared" si="6"/>
+        <v>0.98847807394668941</v>
+      </c>
+      <c r="S12"/>
+      <c r="T12" s="17">
+        <f t="shared" ref="T12:U12" si="7">AVERAGE(T2:T11)</f>
+        <v>0.33024146347611955</v>
+      </c>
+      <c r="U12" s="17">
+        <f t="shared" si="7"/>
+        <v>0.71724137931034482</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="J13" s="14">
+        <f>J12+K12</f>
+        <v>2438.7999999999997</v>
+      </c>
+      <c r="L13" s="15">
+        <f>I12+L12</f>
+        <v>66.2</v>
       </c>
     </row>
   </sheetData>
@@ -3349,17 +4937,18 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:O12"/>
+  <dimension ref="A1:U13"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.33203125" style="1" customWidth="1"/>
     <col min="2" max="12" width="12.6640625" style="1"/>
     <col min="13" max="13" width="16.77734375" style="1" customWidth="1"/>
     <col min="15" max="15" width="12.6640625" style="2"/>
-    <col min="16" max="16384" width="12.6640625" style="1"/>
+    <col min="16" max="16" width="12.6640625" style="1"/>
+    <col min="22" max="16384" width="12.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -3403,8 +4992,20 @@
       <c r="O1" s="5" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="R1" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>2355</v>
       </c>
@@ -3449,8 +5050,24 @@
         <f t="shared" ref="O2:O9" si="1">G2/A2</f>
         <v>0.91974522292993632</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q2">
+        <f>J2/(J2+K2)</f>
+        <v>0.94866169372531817</v>
+      </c>
+      <c r="R2">
+        <f>J2/2326</f>
+        <v>0.92949269131556322</v>
+      </c>
+      <c r="T2">
+        <f>I2/(I2+L2)</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="U2">
+        <f>I2/29</f>
+        <v>0.13793103448275862</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>2355</v>
       </c>
@@ -3495,8 +5112,24 @@
         <f t="shared" si="1"/>
         <v>0.90530785562632698</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q3">
+        <f t="shared" ref="Q3:Q11" si="2">J3/(J3+K3)</f>
+        <v>0.94879786286731971</v>
+      </c>
+      <c r="R3">
+        <f t="shared" ref="R3:R11" si="3">J3/2326</f>
+        <v>0.91616509028374893</v>
+      </c>
+      <c r="T3">
+        <f t="shared" ref="T3:T11" si="4">I3/(I3+L3)</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="U3">
+        <f t="shared" ref="U3:U11" si="5">I3/29</f>
+        <v>3.4482758620689655E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>2355</v>
       </c>
@@ -3541,8 +5174,24 @@
         <f t="shared" si="1"/>
         <v>0.92611464968152868</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q4">
+        <f t="shared" si="2"/>
+        <v>0.95638766519823792</v>
+      </c>
+      <c r="R4">
+        <f t="shared" si="3"/>
+        <v>0.93336199484092863</v>
+      </c>
+      <c r="T4">
+        <f t="shared" si="4"/>
+        <v>0.45454545454545453</v>
+      </c>
+      <c r="U4">
+        <f t="shared" si="5"/>
+        <v>0.34482758620689657</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>2355</v>
       </c>
@@ -3587,8 +5236,24 @@
         <f t="shared" si="1"/>
         <v>0.93545647558386413</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q5">
+        <f t="shared" si="2"/>
+        <v>0.961369622475856</v>
+      </c>
+      <c r="R5">
+        <f t="shared" si="3"/>
+        <v>0.94153052450558894</v>
+      </c>
+      <c r="T5">
+        <f t="shared" si="4"/>
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="U5">
+        <f t="shared" si="5"/>
+        <v>0.44827586206896552</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>2355</v>
       </c>
@@ -3633,8 +5298,24 @@
         <f t="shared" si="1"/>
         <v>0.9545647558386412</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q6">
+        <f t="shared" si="2"/>
+        <v>0.94194362641985696</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="3"/>
+        <v>0.96259673258813416</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="4"/>
+        <v>0.40909090909090912</v>
+      </c>
+      <c r="U6">
+        <f t="shared" si="5"/>
+        <v>0.31034482758620691</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>2355</v>
       </c>
@@ -3679,8 +5360,24 @@
         <f t="shared" si="1"/>
         <v>0.93333333333333335</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q7">
+        <f t="shared" si="2"/>
+        <v>0.95202791103358042</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="3"/>
+        <v>0.93852106620808251</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="4"/>
+        <v>0.34883720930232559</v>
+      </c>
+      <c r="U7">
+        <f t="shared" si="5"/>
+        <v>0.51724137931034486</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>2355</v>
       </c>
@@ -3725,8 +5422,24 @@
         <f t="shared" si="1"/>
         <v>0.90573248407643314</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q8">
+        <f t="shared" si="2"/>
+        <v>0.94788418708240529</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="3"/>
+        <v>0.91487532244196046</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="4"/>
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="U8">
+        <f t="shared" si="5"/>
+        <v>0.17241379310344829</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>2355</v>
       </c>
@@ -3771,8 +5484,24 @@
         <f t="shared" si="1"/>
         <v>0.92569002123142252</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q9">
+        <f t="shared" si="2"/>
+        <v>0.95085563843791132</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="3"/>
+        <v>0.93164230438521067</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="4"/>
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="U9">
+        <f t="shared" si="5"/>
+        <v>0.44827586206896552</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>2355</v>
       </c>
@@ -3817,8 +5546,24 @@
         <f>G10/A10</f>
         <v>0.94140127388535033</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q10">
+        <f t="shared" si="2"/>
+        <v>0.95047784535186797</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="3"/>
+        <v>0.94067067927772996</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="4"/>
+        <v>0.26363636363636361</v>
+      </c>
+      <c r="U10">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>2355</v>
       </c>
@@ -3863,8 +5608,24 @@
         <f>G11/A11</f>
         <v>0.92611464968152868</v>
       </c>
-    </row>
-    <row r="12" spans="1:15" s="6" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="Q11">
+        <f t="shared" si="2"/>
+        <v>0.95679012345679015</v>
+      </c>
+      <c r="R11">
+        <f t="shared" si="3"/>
+        <v>0.93293207222699914</v>
+      </c>
+      <c r="T11">
+        <f t="shared" si="4"/>
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="U11">
+        <f t="shared" si="5"/>
+        <v>0.37931034482758619</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" s="6" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="11">
         <v>2571</v>
       </c>
@@ -3912,6 +5673,33 @@
       <c r="O12" s="9">
         <f>AVERAGE(O2:O11)</f>
         <v>0.9273460721868364</v>
+      </c>
+      <c r="Q12" s="17">
+        <f t="shared" ref="Q12:R12" si="6">AVERAGE(Q2:Q11)</f>
+        <v>0.95151961760491433</v>
+      </c>
+      <c r="R12" s="17">
+        <f t="shared" si="6"/>
+        <v>0.93417884780739457</v>
+      </c>
+      <c r="S12"/>
+      <c r="T12" s="17">
+        <f t="shared" ref="T12:U12" si="7">AVERAGE(T2:T11)</f>
+        <v>0.45177766032417194</v>
+      </c>
+      <c r="U12" s="17">
+        <f t="shared" si="7"/>
+        <v>0.37931034482758619</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="J13" s="14">
+        <f>J12+K12</f>
+        <v>2283.7000000000003</v>
+      </c>
+      <c r="L13" s="15">
+        <f>I12+L12</f>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
